--- a/data/trans_orig/IP07C12-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C12-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2007 (tasa de respuesta: 89,59%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2007 (tasa de respuesta: 89,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26736</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>21177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31923</t>
+          <t>31446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40140</t>
+          <t>40666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55761</t>
+          <t>55748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21554</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36257</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>86102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108062</t>
+          <t>108793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104689</t>
+          <t>104632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128075</t>
+          <t>128130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197579</t>
+          <t>196988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229627</t>
+          <t>229727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55115</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76093</t>
+          <t>75746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59486</t>
+          <t>59410</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81841</t>
+          <t>82164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121362</t>
+          <t>122402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151149</t>
+          <t>153433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29882</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35781</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39728</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60847</t>
+          <t>60665</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23603</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35228</t>
+          <t>35434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30185</t>
+          <t>30923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46328</t>
+          <t>44684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62612</t>
+          <t>61835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39693</t>
+          <t>40020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135123</t>
+          <t>135102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>161467</t>
+          <t>162667</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153625</t>
+          <t>153294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181696</t>
+          <t>180354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>295884</t>
+          <t>296265</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>335569</t>
+          <t>334936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85801</t>
+          <t>85757</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111881</t>
+          <t>112550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>85103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111845</t>
+          <t>111615</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,47 +2941,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>196888</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>178597</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>216615</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>32,91%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>29,86%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>36,21%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>196888</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>179401</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>215682</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>32,91%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>32011</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>52021</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>89667</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23125</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>35552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28492</t>
+          <t>28199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43721</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20795</t>
+          <t>21545</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>21720</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96944</t>
+          <t>96854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120789</t>
+          <t>120788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115726</t>
+          <t>115363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140029</t>
+          <t>140453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219391</t>
+          <t>218804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254116</t>
+          <t>252699</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>54977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78845</t>
+          <t>78007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65326</t>
+          <t>64543</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88260</t>
+          <t>87491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126845</t>
+          <t>128624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159537</t>
+          <t>160755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27209</t>
+          <t>26942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32122</t>
+          <t>31517</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29691</t>
+          <t>29819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42852</t>
+          <t>42236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37651</t>
+          <t>37236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59883</t>
+          <t>58850</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77496</t>
+          <t>76313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>22344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41902</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159390</t>
+          <t>159205</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>188044</t>
+          <t>187305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168737</t>
+          <t>167659</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197669</t>
+          <t>197700</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>335458</t>
+          <t>335088</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>375621</t>
+          <t>375950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>83211</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111135</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95524</t>
+          <t>95968</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>122069</t>
+          <t>122949</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,47 +5900,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>205119</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>186679</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>225558</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>32,18%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>29,29%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>205119</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>185450</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>224222</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>32,18%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47554</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57307</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83439</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>18928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24286</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37685</t>
+          <t>37607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34969</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114644</t>
+          <t>113319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140946</t>
+          <t>139462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112334</t>
+          <t>111721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137196</t>
+          <t>137393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232521</t>
+          <t>232221</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270095</t>
+          <t>270372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75950</t>
+          <t>76061</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100416</t>
+          <t>101643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71286</t>
+          <t>70352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95460</t>
+          <t>94777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152695</t>
+          <t>153843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189544</t>
+          <t>189555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>32489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59709</t>
+          <t>59873</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34478</t>
+          <t>34196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47773</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40029</t>
+          <t>39398</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53746</t>
+          <t>53485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77606</t>
+          <t>79320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97934</t>
+          <t>98529</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>31342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49858</t>
+          <t>48618</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21993</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167410</t>
+          <t>167370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198310</t>
+          <t>197316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170115</t>
+          <t>172859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204679</t>
+          <t>203809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>347809</t>
+          <t>349969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>392516</t>
+          <t>393692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99899</t>
+          <t>101754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129428</t>
+          <t>131135</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>107317</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>138193</t>
+          <t>137237</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217401</t>
+          <t>217072</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259018</t>
+          <t>259367</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28568</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48037</t>
+          <t>48060</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>58028</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83184</t>
+          <t>84058</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -9148,54 +9148,54 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5545</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C12-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C12-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2007 (tasa de respuesta: 89,59%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella, percibida por el/la menor en 2007 (tasa de respuesta: 89,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26683</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21139</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31648</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>48,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21664</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16137</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26736</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16222</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26571</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>47,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26683</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21177</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31446</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>61,73%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40666</t>
+          <t>40375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55748</t>
+          <t>55616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10454</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6292</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16088</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18311</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13657</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24096</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13158</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23584</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10454</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6264</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15612</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>24,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -953,67 +953,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>6087</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2860</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10540</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>6039</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3237</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10681</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,12%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6087</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2849</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10497</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>116259</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>104211</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>127825</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>97180</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>86102</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>108793</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>86833</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>107424</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>116259</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>104632</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>128130</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196988</t>
+          <t>197179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229727</t>
+          <t>228654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70679</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60409</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82094</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>65552</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55058</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75746</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55370</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75600</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,67%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70679</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>59410</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82164</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122402</t>
+          <t>121336</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153433</t>
+          <t>152832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27732</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19766</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37226</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,18%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22373</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16323</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30204</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16328</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>30193</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>11,83%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27732</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20880</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37214</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40371</t>
+          <t>39978</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60665</t>
+          <t>61255</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2615</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6866</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4806</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1328</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4729</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4761</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>216635</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>216635</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>216635</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>189048</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>189048</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>189048</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>216635</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>216635</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>216635</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24396</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18636</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30461</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>49,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29425</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23764</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35434</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23239</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35206</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>54,24%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24396</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18841</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30923</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>49,75%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44684</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61835</t>
+          <t>62081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16593</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11283</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22157</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>15298</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10313</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>20461</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>10300</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>28,2%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>16593</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>11255</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>21993</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40020</t>
+          <t>39573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4518</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12964</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26,44%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>5958</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2964</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10302</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3009</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10565</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>10,98%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,99%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8052</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4404</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13244</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3565</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7673</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7874</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>6,57%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>167338</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>152366</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>180870</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>49,33%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,55%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>148270</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>135102</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>162667</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>134090</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>161422</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>51,25%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>46,7%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>167338</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>153294</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>180354</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>296265</t>
+          <t>296662</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>334936</t>
+          <t>335383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>97726</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>84406</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>110749</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>27,32%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>35,85%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>99162</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>85757</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>112550</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>87203</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>113039</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>34,28%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>97726</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>85103</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>111615</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>178597</t>
+          <t>179011</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>216615</t>
+          <t>214171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>41870</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>33249</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>51467</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>34369</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>25806</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>44105</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>26625</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>43831</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>11,88%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>41870</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>32011</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>52021</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>64283</t>
+          <t>63319</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>88779</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>6179</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2914</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>11223</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>12295</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2,14%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4602</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3220,72 +3220,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3489</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1328</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4619</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3171</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>308899</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>308899</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>308899</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>430</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>289309</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>289309</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>289309</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>308899</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>308899</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>308899</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella, percibida por el/la menor en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22507</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17405</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28214</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29629</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24181</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35552</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23822</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36011</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22507</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16692</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28199</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>49,84%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43909</t>
+          <t>43662</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60728</t>
+          <t>60167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14917</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9783</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20119</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13037</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8625</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19354</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8068</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18677</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14917</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9740</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20801</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>36142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6703</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3395</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11935</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>26,43%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8163</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4274</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13501</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13906</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6703</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2899</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11730</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -4020,72 +4020,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3569</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>798</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4962</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3937</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>128068</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>116970</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>139937</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>107925</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>96854</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>120788</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>96558</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>119661</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>128068</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>115363</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>140453</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,98%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218804</t>
+          <t>219409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252699</t>
+          <t>252233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76395</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65224</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>87369</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66967</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>54977</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78007</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55569</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>77432</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76395</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>64543</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87491</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,99%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128624</t>
+          <t>127682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>160755</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19076</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12803</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26675</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>21566</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14625</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29830</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15075</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>30042</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,85%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19076</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13057</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>26942</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31517</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51402</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1226</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3814</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2375</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7068</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7178</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>198832</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>198832</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>198832</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31695</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25620</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37307</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,45%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>36334</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29819</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42236</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29862</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>31695</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>25488</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>37236</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58850</t>
+          <t>58964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76313</t>
+          <t>76631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17637</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12699</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23627</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16167</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10916</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22344</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11073</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>22208</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>17637</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>12268</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23837</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26308</t>
+          <t>26092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41667</t>
+          <t>42288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2808</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10034</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>7461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3679</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12501</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3807</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12812</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>12,27%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5878</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2853</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>10129</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -5389,102 +5389,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>839</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4174</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4179</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4639</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1781</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5428</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>182270</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>168828</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>197041</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>55,9%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51,78%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,43%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>173888</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>159205</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>187305</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>158923</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>188447</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>55,87%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>60,18%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>182270</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>167659</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>197700</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>335088</t>
+          <t>336027</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>375950</t>
+          <t>377882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>108948</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>96215</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>123237</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>33,41%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>37,79%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>96170</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>83959</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>110781</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>83078</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>108714</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>30,9%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>35,59%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>108948</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>95968</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>122949</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>33,41%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>186679</t>
+          <t>184502</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>225558</t>
+          <t>224810</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>31656</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22942</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>40877</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>37189</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>28396</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>47528</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>28817</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>48212</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>11,95%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>31656</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>23293</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>41613</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>57099</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>83736</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -6071,67 +6071,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6992</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>4012</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8894</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1473</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8568</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7999</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>311258</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>311258</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>311258</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella, percibida por el/la menor en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16125</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11321</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21096</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14263</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9963</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18928</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9748</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19009</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16125</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11236</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21730</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>24209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37607</t>
+          <t>37443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,68%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17242</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12492</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22897</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10696</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6320</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15388</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6781</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15391</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>34,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17242</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12089</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22306</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>35132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2646</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,64%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3730</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7778</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7879</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,19%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>25,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2646</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5784</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -6979,72 +6979,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1918</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5139</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>125110</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>112409</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>137392</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>127157</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>113319</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>139462</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>114273</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>141253</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>125110</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>111721</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>137393</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,29%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232221</t>
+          <t>233209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270372</t>
+          <t>270252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,51%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>82997</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70293</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94726</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>87496</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76061</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>101643</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>75333</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100305</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,94%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>82997</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70352</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>94777</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153843</t>
+          <t>152485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189555</t>
+          <t>187230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24231</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17801</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33527</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>24021</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16651</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>32971</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16768</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>32641</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,87%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>24231</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17400</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32489</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59873</t>
+          <t>60036</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -7661,102 +7661,102 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2446</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3482</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1362</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8168</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7764</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>5928</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2669</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>11237</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2446</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8060</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>5928</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2571</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>11232</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7774,107 +7774,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1279</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4302</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4095</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>234784</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>234784</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>234784</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>243434</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>243434</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>243434</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>234784</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>234784</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>234784</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47104</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>39876</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53624</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>71,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>41451</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34196</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>48086</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34561</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47663</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>47104</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>39398</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53485</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>62,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79320</t>
+          <t>78454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98529</t>
+          <t>98192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22931</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29265</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>17083</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11495</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23699</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11983</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24174</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>24,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22931</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17102</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30166</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31342</t>
+          <t>31286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48618</t>
+          <t>49572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5467</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2681</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9753</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9816</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5520</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15437</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5884</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15830</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,08%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5467</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2571</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>10064</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22103</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -8343,107 +8343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4909</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3678</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3741</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -8456,107 +8456,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>69734</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>69734</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>69734</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>188339</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>173687</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>202990</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,29%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>50,06%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,51%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>182870</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>167370</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>197316</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>168287</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>200294</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>53,19%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48,69%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>188339</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>172859</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>203809</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>54,29%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>349969</t>
+          <t>349956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>393692</t>
+          <t>394399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>123169</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>107337</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>137580</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>39,66%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>115274</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>101754</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>131135</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>100742</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>131459</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>33,53%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>38,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>123169</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>107317</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>137237</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217072</t>
+          <t>215634</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259367</t>
+          <t>259216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>32344</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>24407</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>41874</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>37567</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>28455</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>48060</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>28704</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>48385</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>10,93%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>32344</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>24820</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>42412</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58028</t>
+          <t>57328</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>84058</t>
+          <t>84693</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3072</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7531</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>6138</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>11489</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>11501</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7801</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1925</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5545</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>346924</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>346924</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>346924</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>490</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>343774</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>343774</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>343774</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
